--- a/SK 05 - AssistantAPI AGENT full (plugin, codeinterpreter, filesearch)/data/codeinterpreter_files/turbines.xlsx
+++ b/SK 05 - AssistantAPI AGENT full (plugin, codeinterpreter, filesearch)/data/codeinterpreter_files/turbines.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\mauromi\source\git_repos\semantic-kernel\SK 05 - AssistantAPI AGENT with AzureAssistantAgent (kernel AND plugin)\data\codeinterpreter_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\mauromi\source\git_repos\semantic-kernel\SK 05 - AssistantAPI AGENT full (plugin, codeinterpreter, filesearch)\data\codeinterpreter_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E97133A-801F-4253-B768-53586D22DBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59004057-81CF-434F-9A5F-BF86561E93E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0E4C459-3827-4FDF-A5D1-F63FD1112017}"/>
   </bookViews>
@@ -585,7 +585,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8980A5C6-6184-47F1-BE58-7B12F2989C54}" name="Table2" displayName="Table2" ref="A1:E22" totalsRowShown="0">
-  <autoFilter ref="A1:E22" xr:uid="{8980A5C6-6184-47F1-BE58-7B12F2989C54}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{D58B881A-1E6E-49FC-B61A-78186740428D}" name="Turbine_ID"/>
     <tableColumn id="2" xr3:uid="{4FC7EBD1-75AE-4211-B34E-6E2DF9466F37}" name="Wind_Speed"/>
@@ -593,7 +592,7 @@
     <tableColumn id="4" xr3:uid="{7096F4D3-80AF-40A3-AE45-39531E6DA573}" name="Voltage"/>
     <tableColumn id="5" xr3:uid="{1B188E3F-F24B-46D0-851A-DD124043AF6E}" name="Maintenance_Date" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleDark11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium23" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1303,4 +1302,10 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f42aa342-8706-4288-bd11-ebb85995028c}" enabled="1" method="Standard" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>